--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2a2c3e65ebc041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rdcf5ea5902924441"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R81ba6b314cb94247"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rca11b49a73074eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R916e857f4be44a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R986bcf80bbf24997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R6c8825a5526e420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Raa0d0f7269f54939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R2efb77b50a034b1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R3704ac41424a4167"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -380,7 +380,7 @@
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>浏览器验收测试</x:v>
+        <x:v>浏览器核查测试</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
         <x:v>output/tests/account_security_totp.spec.ts</x:v>
@@ -389,7 +389,7 @@
         <x:v>TypeScript</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>安全平台工程师维护账号冻结验收流程</x:v>
+        <x:v>安全平台工程师维护账号冻结检查流程</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -746,7 +746,7 @@
     </x:row>
     <x:row r="8" ht="92" customHeight="1">
       <x:c r="A8" s="9" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
         <x:v>output/playwright.config.ts,output/tests/account_security_totp.spec.ts,output/reports/decision_matrix.csv,output/reports/totp_window.csv,output/reports/network_receipts.csv,output/reports/modal_focus.csv</x:v>
@@ -755,7 +755,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>交付物答案清单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R986bcf80bbf24997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R6c8825a5526e420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Raa0d0f7269f54939"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R2efb77b50a034b1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R3704ac41424a4167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R81d0457e6d9e4894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R380e88468f574773"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9a95953d07ea4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R498facb5ac4c44e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R6e1ebd07ea2440e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -355,7 +355,7 @@
         <x:v>交付物名称</x:v>
       </x:c>
       <x:c r="B1" s="16" t="str">
-        <x:v>固定路径或命名规则</x:v>
+        <x:v>固定路径/命名规则</x:v>
       </x:c>
       <x:c r="C1" s="16" t="str">
         <x:v>格式</x:v>
@@ -1023,7 +1023,7 @@
         <x:v>变量名、注释、空白和内部数据结构可以不同</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>不修改输入，不访问外部服务，不按样本主键写死裁决</x:v>
+        <x:v>不修改输入，不访问外部服务，不按当前业务主键写死裁决</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
